--- a/02_DIA_inicio_2026_analisis_assets/rbd_9727_escuela-ciudad-de-barcelona_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9727_escuela-ciudad-de-barcelona_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9571FDF4-D1F4-4B42-99E3-4A88E45D037D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE9C195D-3A39-4C33-AA53-2A440B1B2DAD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C106834-B8CD-4FEB-8F55-04B89069FDF0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67A5B8BB-2E8D-44A2-89DE-D28AE885A483}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E088D865-3D78-442F-B41F-34C4FD196DE3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7D14CB8-8116-4221-8712-9A77C4CFCBE8}"/>
 </file>